--- a/content/course_schedule.xlsx
+++ b/content/course_schedule.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GG\Msc\DATA9910 (23115C)_working_with_data_lucas_rizzo_10ects_Thurs\github\wwd_9910_thurs\content\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC6F55E-B18D-4488-8AB1-6C6B12C6B26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,15 +25,230 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
+  <si>
+    <t>Week 1</t>
+  </si>
+  <si>
+    <t>Set up environment and R notebook</t>
+  </si>
+  <si>
+    <t>Week 2</t>
+  </si>
+  <si>
+    <t>Review Python and practice</t>
+  </si>
+  <si>
+    <t>Week 3</t>
+  </si>
+  <si>
+    <t>Review R</t>
+  </si>
+  <si>
+    <t>Importing data with R</t>
+  </si>
+  <si>
+    <t>Week 4</t>
+  </si>
+  <si>
+    <t>Intro SQL and aggregate queries</t>
+  </si>
+  <si>
+    <t>Week 5</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Databases and scripting languages </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>To be submitted</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Week 6</t>
+  </si>
+  <si>
+    <t>Interpreting Data (summary statistics, data visualisation)</t>
+  </si>
+  <si>
+    <t>Week 7</t>
+  </si>
+  <si>
+    <t>Review week</t>
+  </si>
+  <si>
+    <t>Week 8</t>
+  </si>
+  <si>
+    <t>Data manipulation in R</t>
+  </si>
+  <si>
+    <t>Pandas and Numpy</t>
+  </si>
+  <si>
+    <t>Week 9</t>
+  </si>
+  <si>
+    <t>Data visualisation in Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data processing (regular expressions) </t>
+  </si>
+  <si>
+    <t>Week 10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Audio data (R and tuneR) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>To be submitted</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Week 11</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Image data (Python and skimage) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>To be submitted</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFE06666"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Week 12</t>
+  </si>
+  <si>
+    <t>Time series (Python and Pandas)</t>
+  </si>
+  <si>
+    <t>Week 13</t>
+  </si>
+  <si>
+    <t>Working on Assignment</t>
+  </si>
+  <si>
+    <t>Assignment deadline</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFE06666"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFE06666"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +259,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +267,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +582,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B3:C19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="54.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="3"/>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B18:B19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740BF701-752D-48E7-9EED-046B8BDF9E51}">
+  <dimension ref="B2:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="3"/>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B17:B18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/content/course_schedule.xlsx
+++ b/content/course_schedule.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GG\Msc\DATA9910 (23115C)_working_with_data_lucas_rizzo_10ects_Thurs\github\wwd_9910_thurs\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC6F55E-B18D-4488-8AB1-6C6B12C6B26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52265B53-7D8B-4F1A-8860-474130CF1896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26205" yWindow="465" windowWidth="24840" windowHeight="14430" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="w9" sheetId="2" r:id="rId2"/>
+    <sheet name="w10-audio-data" sheetId="3" r:id="rId3"/>
+    <sheet name="w11-images-27thnov25" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="30">
   <si>
     <t>Week 1</t>
   </si>
@@ -294,13 +296,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +609,7 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -615,7 +617,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
@@ -653,7 +655,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -661,13 +663,13 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -675,8 +677,8 @@
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -705,7 +707,7 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -713,8 +715,8 @@
       </c>
     </row>
     <row r="19" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -755,7 +757,7 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -763,7 +765,7 @@
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
@@ -801,7 +803,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -809,13 +811,13 @@
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -823,8 +825,8 @@
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -853,7 +855,7 @@
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -861,8 +863,304 @@
       </c>
     </row>
     <row r="18" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7812DFC-A98D-457B-864D-D04264E1BA3F}">
+  <dimension ref="B3:C19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="65.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="5"/>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="5"/>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="5"/>
+      <c r="C19" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B18:B19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA97AF7-20A7-434B-9BC9-5D46FB16D749}">
+  <dimension ref="B2:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="47.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="5"/>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="5"/>
+      <c r="C18" s="4" t="s">
         <v>29</v>
       </c>
     </row>

--- a/content/course_schedule.xlsx
+++ b/content/course_schedule.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GG\Msc\DATA9910 (23115C)_working_with_data_lucas_rizzo_10ects_Thurs\github\wwd_9910_thurs\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52265B53-7D8B-4F1A-8860-474130CF1896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD535CFC-A6C6-41EF-B78D-E64F9F4280E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26205" yWindow="465" windowWidth="24840" windowHeight="14430" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1665" yWindow="795" windowWidth="20700" windowHeight="11940" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="w9" sheetId="2" r:id="rId2"/>
     <sheet name="w10-audio-data" sheetId="3" r:id="rId3"/>
     <sheet name="w11-images-27thnov25" sheetId="4" r:id="rId4"/>
+    <sheet name="w12-time-series" sheetId="5" r:id="rId5"/>
+    <sheet name="maths" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="57">
   <si>
     <t>Week 1</t>
   </si>
@@ -209,12 +211,93 @@
   <si>
     <t>Assignment deadline</t>
   </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>What happens if the effect exists?</t>
+  </si>
+  <si>
+    <t>Interpretation</t>
+  </si>
+  <si>
+    <t>You detect it 4 out of 5 times</t>
+  </si>
+  <si>
+    <t>Acceptable but still 1 in 5 chance you’d miss it</t>
+  </si>
+  <si>
+    <t>You detect it 9 out of 10 times</t>
+  </si>
+  <si>
+    <t>Much lower risk of overlooking it</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>power calculations for</t>
+  </si>
+  <si>
+    <t>pwr.2p.test</t>
+  </si>
+  <si>
+    <t>two proportions (equal n)</t>
+  </si>
+  <si>
+    <t>pwr.2p2n.test</t>
+  </si>
+  <si>
+    <t>two proportions (unequal n)</t>
+  </si>
+  <si>
+    <t>pwr.anova.test</t>
+  </si>
+  <si>
+    <t>balanced one way ANOVA</t>
+  </si>
+  <si>
+    <t>pwr.chisq.test</t>
+  </si>
+  <si>
+    <t>chi-square test</t>
+  </si>
+  <si>
+    <t>pwr.f2.test</t>
+  </si>
+  <si>
+    <t>general linear model</t>
+  </si>
+  <si>
+    <t>pwr.p.test</t>
+  </si>
+  <si>
+    <t>proportion (one sample)</t>
+  </si>
+  <si>
+    <t>pwr.r.test</t>
+  </si>
+  <si>
+    <t>correlation</t>
+  </si>
+  <si>
+    <t>pwr.t.test</t>
+  </si>
+  <si>
+    <t>t-tests (one sample, 2 sample, paired)</t>
+  </si>
+  <si>
+    <t>pwr.t2n.test</t>
+  </si>
+  <si>
+    <t>t-test (two samples with unequal n)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,13 +335,36 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -288,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -305,6 +411,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1173,4 +1291,308 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C683B6-6274-414E-BF40-26023B44B15F}">
+  <dimension ref="B2:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="5"/>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="5"/>
+      <c r="C18" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B17:B18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E93C2902-2ACD-4AD7-8B0D-69E6AECF40FC}">
+  <dimension ref="B3:D23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="6"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>